--- a/Fiche de mouvement _09-2026.xlsx
+++ b/Fiche de mouvement _09-2026.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\OneDrive\Documents\Samir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{12ECEBE3-12B9-45F7-B6B3-00DF805E5005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32DFA259-9809-4932-8A6A-4F3DC656C53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
   </bookViews>
   <sheets>
     <sheet name="DASHBOARD" sheetId="1" r:id="rId1"/>
     <sheet name="01-09" sheetId="2" r:id="rId2"/>
+    <sheet name="02-09" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
   <si>
     <t>Date</t>
   </si>
@@ -91,6 +92,9 @@
     <t>Vol</t>
   </si>
   <si>
+    <t>20</t>
+  </si>
+  <si>
     <t>SORTIE</t>
   </si>
   <si>
@@ -110,6 +114,21 @@
   </si>
   <si>
     <t>NO° Scellé</t>
+  </si>
+  <si>
+    <t>ECMU512820/2</t>
+  </si>
+  <si>
+    <t>000204-598-31</t>
+  </si>
+  <si>
+    <t>CAIU634538 /3</t>
+  </si>
+  <si>
+    <t>J1803692</t>
+  </si>
+  <si>
+    <t>0723ICS0013</t>
   </si>
 </sst>
 </file>
@@ -284,7 +303,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -353,11 +372,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -417,9 +451,6 @@
     <xf numFmtId="166" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -494,6 +525,15 @@
     </xf>
     <xf numFmtId="14" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -919,15 +959,15 @@
       </c>
       <c r="B2" s="3">
         <f>'01-09'!H1</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3">
         <f>'01-09'!H2</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="4">
         <f t="shared" ref="D2:D22" si="0">SUM(B2:C2)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" s="3"/>
     </row>
@@ -1120,15 +1160,15 @@
       </c>
       <c r="B24" s="5">
         <f>SUM(B2:B22)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24" s="5">
         <f>SUM(C2:C22)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" s="5">
         <f>SUM(D2:D22)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -1144,23 +1184,23 @@
   <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" style="23" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" style="23" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="23" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="11.42578125" style="23"/>
-    <col min="11" max="11" width="14.7109375" style="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="11.42578125" style="23"/>
+    <col min="1" max="1" width="3.140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="22" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="22" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="22" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="22" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="22"/>
+    <col min="11" max="11" width="14.7109375" style="22" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="H1" s="8">
         <f>COUNTIF(C8:C20,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1" s="9" t="s">
         <v>6</v>
@@ -1177,7 +1217,7 @@
       </c>
       <c r="H2" s="8">
         <f>COUNTA(C25:C30)-CE2</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>6</v>
@@ -1215,7 +1255,7 @@
       <c r="A6" s="6"/>
       <c r="B6" s="14"/>
     </row>
-    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
         <v>10</v>
       </c>
@@ -1239,156 +1279,166 @@
       <c r="A8" s="18">
         <v>1</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="22"/>
+      <c r="B8" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="20">
+        <v>1092026</v>
+      </c>
+      <c r="D8" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="21"/>
     </row>
     <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="18">
         <v>2</v>
       </c>
-      <c r="B9" s="46"/>
+      <c r="B9" s="45"/>
       <c r="C9" s="20"/>
-      <c r="D9" s="25"/>
+      <c r="D9" s="24"/>
       <c r="E9" s="19"/>
       <c r="F9" s="19"/>
-      <c r="G9" s="22"/>
+      <c r="G9" s="21"/>
     </row>
     <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="18">
         <v>3</v>
       </c>
-      <c r="B10" s="46"/>
+      <c r="B10" s="45"/>
       <c r="C10" s="20"/>
       <c r="D10" s="19"/>
       <c r="E10" s="19"/>
       <c r="F10" s="19"/>
-      <c r="G10" s="22"/>
+      <c r="G10" s="21"/>
     </row>
     <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="18">
         <v>4</v>
       </c>
-      <c r="B11" s="46"/>
+      <c r="B11" s="45"/>
       <c r="C11" s="20"/>
       <c r="D11" s="19"/>
       <c r="E11" s="19"/>
       <c r="F11" s="19"/>
-      <c r="G11" s="22"/>
+      <c r="G11" s="21"/>
     </row>
     <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="18">
         <v>5</v>
       </c>
-      <c r="B12" s="46"/>
+      <c r="B12" s="45"/>
       <c r="C12" s="20"/>
       <c r="D12" s="19"/>
-      <c r="E12" s="26"/>
+      <c r="E12" s="25"/>
       <c r="F12" s="19"/>
-      <c r="G12" s="22"/>
+      <c r="G12" s="21"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="18">
         <v>6</v>
       </c>
-      <c r="B13" s="46"/>
+      <c r="B13" s="45"/>
       <c r="C13" s="20"/>
       <c r="D13" s="19"/>
-      <c r="E13" s="26"/>
+      <c r="E13" s="25"/>
       <c r="F13" s="19"/>
-      <c r="G13" s="22"/>
+      <c r="G13" s="21"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="18">
         <v>7</v>
       </c>
-      <c r="B14" s="46"/>
+      <c r="B14" s="45"/>
       <c r="C14" s="20"/>
       <c r="D14" s="19"/>
-      <c r="E14" s="26"/>
+      <c r="E14" s="25"/>
       <c r="F14" s="19"/>
-      <c r="G14" s="22"/>
+      <c r="G14" s="21"/>
     </row>
     <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="18">
         <v>8</v>
       </c>
-      <c r="B15" s="46"/>
+      <c r="B15" s="45"/>
       <c r="C15" s="20"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="25"/>
       <c r="F15" s="19"/>
-      <c r="G15" s="22"/>
+      <c r="G15" s="21"/>
     </row>
     <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="18">
         <v>9</v>
       </c>
-      <c r="B16" s="46"/>
+      <c r="B16" s="45"/>
       <c r="C16" s="20"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="25"/>
       <c r="F16" s="19"/>
-      <c r="G16" s="22"/>
+      <c r="G16" s="21"/>
     </row>
     <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="18">
         <v>10</v>
       </c>
-      <c r="B17" s="46"/>
+      <c r="B17" s="45"/>
       <c r="C17" s="20"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="25"/>
       <c r="F17" s="19"/>
-      <c r="G17" s="22"/>
+      <c r="G17" s="21"/>
     </row>
     <row r="18" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="18">
         <v>11</v>
       </c>
-      <c r="B18" s="24"/>
+      <c r="B18" s="23"/>
       <c r="C18" s="20"/>
       <c r="D18" s="19"/>
-      <c r="E18" s="26"/>
+      <c r="E18" s="25"/>
       <c r="F18" s="19"/>
-      <c r="G18" s="22"/>
+      <c r="G18" s="21"/>
     </row>
     <row r="19" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="18">
         <v>12</v>
       </c>
-      <c r="B19" s="24"/>
+      <c r="B19" s="23"/>
       <c r="C19" s="20"/>
       <c r="D19" s="19"/>
       <c r="E19" s="19"/>
       <c r="F19" s="19"/>
-      <c r="G19" s="22"/>
+      <c r="G19" s="21"/>
     </row>
     <row r="20" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="18"/>
-      <c r="B20" s="28"/>
+      <c r="B20" s="27"/>
       <c r="C20" s="20"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="22"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="21"/>
     </row>
     <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
-      <c r="B21" s="22"/>
+      <c r="B21" s="21"/>
       <c r="C21" s="7"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
       <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
       <c r="B22" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1404,10 +1454,10 @@
         <v>10</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D24" s="16" t="s">
         <v>13</v>
@@ -1420,95 +1470,105 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="29">
+      <c r="A25" s="28">
         <v>1</v>
       </c>
-      <c r="B25" s="20"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="29"/>
+      <c r="B25" s="20">
+        <v>1092026</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="32">
+        <v>3579</v>
+      </c>
+      <c r="F25" s="28">
+        <v>40</v>
+      </c>
     </row>
     <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="29">
+      <c r="A26" s="28">
         <v>2</v>
       </c>
       <c r="B26" s="20"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="29"/>
-      <c r="I26" s="35"/>
-      <c r="J26" s="35"/>
-      <c r="K26" s="35"/>
-      <c r="L26" s="35"/>
-      <c r="M26" s="35"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="28"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="34"/>
+      <c r="K26" s="34"/>
+      <c r="L26" s="34"/>
+      <c r="M26" s="34"/>
     </row>
     <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="29">
+      <c r="A27" s="28">
         <v>3</v>
       </c>
       <c r="B27" s="20"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="29"/>
-      <c r="I27" s="35"/>
-      <c r="J27" s="35"/>
-      <c r="K27" s="35"/>
-      <c r="L27" s="35"/>
-      <c r="M27" s="35"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="28"/>
+      <c r="I27" s="34"/>
+      <c r="J27" s="34"/>
+      <c r="K27" s="34"/>
+      <c r="L27" s="34"/>
+      <c r="M27" s="34"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="29">
+      <c r="A28" s="28">
         <v>4</v>
       </c>
       <c r="B28" s="20"/>
-      <c r="C28" s="37"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="29"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="28"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="29">
+      <c r="A29" s="28">
         <v>5</v>
       </c>
       <c r="B29" s="20"/>
-      <c r="C29" s="37"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="29"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="28"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="29">
+      <c r="A30" s="28">
         <v>6</v>
       </c>
       <c r="B30" s="20"/>
-      <c r="C30" s="37"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="29"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="28"/>
     </row>
     <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="39"/>
-      <c r="B31" s="40"/>
-      <c r="C31" s="41"/>
+      <c r="A31" s="38"/>
+      <c r="B31" s="39"/>
+      <c r="C31" s="40"/>
       <c r="D31"/>
-      <c r="E31" s="42"/>
-      <c r="F31" s="39"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="38"/>
     </row>
     <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="39"/>
-      <c r="B32" s="40"/>
-      <c r="C32" s="41"/>
+      <c r="A32" s="38"/>
+      <c r="B32" s="39"/>
+      <c r="C32" s="40"/>
       <c r="D32"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="39"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="38"/>
     </row>
     <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="6"/>
       <c r="B33" s="12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
@@ -1526,93 +1586,93 @@
         <v>10</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C35" s="16" t="s">
         <v>13</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F35" s="17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="29">
+      <c r="A36" s="28">
         <v>1</v>
       </c>
       <c r="B36" s="20"/>
-      <c r="C36" s="33"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42"/>
     </row>
     <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="29">
+      <c r="A37" s="28">
         <v>2</v>
       </c>
       <c r="B37" s="20"/>
-      <c r="C37" s="38"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="43"/>
-      <c r="F37" s="43"/>
+      <c r="C37" s="37"/>
+      <c r="D37" s="37"/>
+      <c r="E37" s="42"/>
+      <c r="F37" s="42"/>
     </row>
     <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="29">
+      <c r="A38" s="28">
         <v>3</v>
       </c>
       <c r="B38" s="20"/>
-      <c r="C38" s="33"/>
-      <c r="D38" s="33"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="43"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="42"/>
+      <c r="F38" s="42"/>
     </row>
     <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="29">
+      <c r="A39" s="28">
         <v>4</v>
       </c>
       <c r="B39" s="20"/>
-      <c r="C39" s="33"/>
-      <c r="D39" s="33"/>
-      <c r="E39" s="43"/>
-      <c r="F39" s="43"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="42"/>
+      <c r="F39" s="42"/>
     </row>
     <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="29">
+      <c r="A40" s="28">
         <v>5</v>
       </c>
       <c r="B40" s="20"/>
       <c r="C40" s="19"/>
       <c r="D40" s="19"/>
-      <c r="E40" s="43"/>
-      <c r="F40" s="43"/>
+      <c r="E40" s="42"/>
+      <c r="F40" s="42"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="44">
+      <c r="A41" s="43">
         <v>6</v>
       </c>
       <c r="B41" s="20"/>
-      <c r="C41" s="29"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="33"/>
-      <c r="F41" s="33"/>
+      <c r="C41" s="28"/>
+      <c r="D41" s="35"/>
+      <c r="E41" s="32"/>
+      <c r="F41" s="32"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="44">
+      <c r="A42" s="43">
         <v>7</v>
       </c>
       <c r="B42" s="20"/>
-      <c r="C42" s="33"/>
-      <c r="D42" s="29"/>
-      <c r="E42" s="33"/>
-      <c r="F42" s="29"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="28"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="28"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F43" s="45"/>
+      <c r="F43" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1630,4 +1690,13 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74EC856B-C7FE-4404-9D75-FE95EF21C2E2}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Fiche de mouvement _09-2026.xlsx
+++ b/Fiche de mouvement _09-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\OneDrive\Documents\Samir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32DFA259-9809-4932-8A6A-4F3DC656C53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305CBC8F-328A-4A8E-85A0-DA49C8604CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
   </bookViews>
   <sheets>
     <sheet name="DASHBOARD" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="56">
   <si>
     <t>Date</t>
   </si>
@@ -92,6 +92,9 @@
     <t>Vol</t>
   </si>
   <si>
+    <t>40</t>
+  </si>
+  <si>
     <t>20</t>
   </si>
   <si>
@@ -129,6 +132,84 @@
   </si>
   <si>
     <t>0723ICS0013</t>
+  </si>
+  <si>
+    <t>TRLU948903 /4</t>
+  </si>
+  <si>
+    <t>00327-510-31</t>
+  </si>
+  <si>
+    <t>ROWEI I5</t>
+  </si>
+  <si>
+    <t>LSJ--SZ782970</t>
+  </si>
+  <si>
+    <t>LSJ--SZ782961</t>
+  </si>
+  <si>
+    <t>LSJ--SZ783783</t>
+  </si>
+  <si>
+    <t>LSJ--SZ754980</t>
+  </si>
+  <si>
+    <t>LSJ--SZ754107</t>
+  </si>
+  <si>
+    <t>LSJ--SZ754982</t>
+  </si>
+  <si>
+    <t>LSJ--SZ754109</t>
+  </si>
+  <si>
+    <t>TCLU331996 /2</t>
+  </si>
+  <si>
+    <t>0073-512-31</t>
+  </si>
+  <si>
+    <t>VIDE</t>
+  </si>
+  <si>
+    <t>TIIU811908 /0</t>
+  </si>
+  <si>
+    <t>TIIU811819 /1</t>
+  </si>
+  <si>
+    <t>02177-588-31</t>
+  </si>
+  <si>
+    <t>TGBU749046 /1</t>
+  </si>
+  <si>
+    <t>FX48662628</t>
+  </si>
+  <si>
+    <t>FDCU031798 /9</t>
+  </si>
+  <si>
+    <t>FJ27558901</t>
+  </si>
+  <si>
+    <t>0157ICS0016</t>
+  </si>
+  <si>
+    <t>0157ICS0083</t>
+  </si>
+  <si>
+    <t>DRYU939251 /7</t>
+  </si>
+  <si>
+    <t>FDCU009891 /5</t>
+  </si>
+  <si>
+    <t>LG00557484</t>
+  </si>
+  <si>
+    <t>LG00557480</t>
   </si>
 </sst>
 </file>
@@ -139,7 +220,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="##&quot;/&quot;##&quot;/&quot;####"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -232,12 +313,6 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Segoe UI"/>
       <family val="2"/>
     </font>
     <font>
@@ -391,7 +466,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -457,9 +532,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -469,9 +541,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -487,7 +556,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -511,10 +580,10 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -534,6 +603,22 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -596,6 +681,61 @@
         <a:xfrm>
           <a:off x="0" y="3"/>
           <a:ext cx="2000250" cy="476248"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>3</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Image 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BC32A58-E0EC-438C-8359-D84AE7F1F5DA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3"/>
+          <a:ext cx="2000250" cy="523872"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -963,11 +1103,11 @@
       </c>
       <c r="C2" s="3">
         <f>'01-09'!H2</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" s="4">
         <f t="shared" ref="D2:D22" si="0">SUM(B2:C2)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F2" s="3"/>
     </row>
@@ -975,9 +1115,18 @@
       <c r="A3" s="2">
         <v>46267</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4"/>
+      <c r="B3" s="3">
+        <f>'02-09'!H1</f>
+        <v>2</v>
+      </c>
+      <c r="C3" s="3">
+        <f>'02-09'!H1</f>
+        <v>2</v>
+      </c>
+      <c r="D3" s="4">
+        <f t="shared" ref="D3" si="1">SUM(B3:C3)</f>
+        <v>4</v>
+      </c>
       <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -1160,15 +1309,15 @@
       </c>
       <c r="B24" s="5">
         <f>SUM(B2:B22)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C24" s="5">
         <f>SUM(C2:C22)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D24" s="5">
         <f>SUM(D2:D22)</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -1181,7 +1330,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A6E3EF0-42A6-4E9D-BB88-F1F87C40E4D1}">
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" style="22" bestFit="1" customWidth="1"/>
@@ -1199,7 +1348,7 @@
     <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="H1" s="8">
-        <f>COUNTIF(C8:C20,"&lt;&gt;")</f>
+        <f>COUNTIF(C8:C15,"&lt;&gt;")</f>
         <v>1</v>
       </c>
       <c r="I1" s="9" t="s">
@@ -1209,21 +1358,21 @@
     <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="F2" s="8">
-        <f>COUNTIFS(B25:B30,"&lt;&gt;",C25:C30,"VH")</f>
-        <v>0</v>
+        <f>COUNTIFS(B20:B29,"&lt;&gt;",C20:C29,"VH")</f>
+        <v>7</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="8">
-        <f>COUNTA(C25:C30)-CE2</f>
-        <v>1</v>
+        <f>COUNTA(C20:C29)-F2</f>
+        <v>3</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>6</v>
       </c>
       <c r="J2" s="10">
-        <f>COUNTIF(E25:E30,"VIDE")</f>
+        <f>COUNTIF(E20:E29,"VIDE")</f>
         <v>0</v>
       </c>
     </row>
@@ -1279,20 +1428,20 @@
       <c r="A8" s="18">
         <v>1</v>
       </c>
-      <c r="B8" s="48" t="s">
-        <v>28</v>
+      <c r="B8" s="46" t="s">
+        <v>29</v>
       </c>
       <c r="C8" s="20">
         <v>1092026</v>
       </c>
-      <c r="D8" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="46" t="s">
+      <c r="D8" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="47" t="s">
-        <v>16</v>
+      <c r="E8" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="45" t="s">
+        <v>17</v>
       </c>
       <c r="G8" s="21"/>
     </row>
@@ -1300,9 +1449,9 @@
       <c r="A9" s="18">
         <v>2</v>
       </c>
-      <c r="B9" s="45"/>
+      <c r="B9" s="43"/>
       <c r="C9" s="20"/>
-      <c r="D9" s="24"/>
+      <c r="D9" s="23"/>
       <c r="E9" s="19"/>
       <c r="F9" s="19"/>
       <c r="G9" s="21"/>
@@ -1311,7 +1460,7 @@
       <c r="A10" s="18">
         <v>3</v>
       </c>
-      <c r="B10" s="45"/>
+      <c r="B10" s="43"/>
       <c r="C10" s="20"/>
       <c r="D10" s="19"/>
       <c r="E10" s="19"/>
@@ -1322,7 +1471,7 @@
       <c r="A11" s="18">
         <v>4</v>
       </c>
-      <c r="B11" s="45"/>
+      <c r="B11" s="43"/>
       <c r="C11" s="20"/>
       <c r="D11" s="19"/>
       <c r="E11" s="19"/>
@@ -1333,10 +1482,10 @@
       <c r="A12" s="18">
         <v>5</v>
       </c>
-      <c r="B12" s="45"/>
+      <c r="B12" s="43"/>
       <c r="C12" s="20"/>
       <c r="D12" s="19"/>
-      <c r="E12" s="25"/>
+      <c r="E12" s="24"/>
       <c r="F12" s="19"/>
       <c r="G12" s="21"/>
     </row>
@@ -1344,10 +1493,10 @@
       <c r="A13" s="18">
         <v>6</v>
       </c>
-      <c r="B13" s="45"/>
+      <c r="B13" s="43"/>
       <c r="C13" s="20"/>
       <c r="D13" s="19"/>
-      <c r="E13" s="25"/>
+      <c r="E13" s="24"/>
       <c r="F13" s="19"/>
       <c r="G13" s="21"/>
     </row>
@@ -1355,10 +1504,10 @@
       <c r="A14" s="18">
         <v>7</v>
       </c>
-      <c r="B14" s="45"/>
+      <c r="B14" s="43"/>
       <c r="C14" s="20"/>
       <c r="D14" s="19"/>
-      <c r="E14" s="25"/>
+      <c r="E14" s="24"/>
       <c r="F14" s="19"/>
       <c r="G14" s="21"/>
     </row>
@@ -1366,323 +1515,409 @@
       <c r="A15" s="18">
         <v>8</v>
       </c>
-      <c r="B15" s="45"/>
+      <c r="B15" s="43"/>
       <c r="C15" s="20"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="24"/>
       <c r="F15" s="19"/>
       <c r="G15" s="21"/>
     </row>
     <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="18">
-        <v>9</v>
-      </c>
-      <c r="B16" s="45"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="21"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="18">
+      <c r="A17" s="6"/>
+      <c r="B17" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="45"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="21"/>
-    </row>
-    <row r="18" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="18">
-        <v>11</v>
-      </c>
-      <c r="B18" s="23"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="21"/>
-    </row>
-    <row r="19" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="18">
-        <v>12</v>
-      </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="21"/>
-    </row>
-    <row r="20" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="18"/>
-      <c r="B20" s="27"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="21"/>
-    </row>
-    <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="6"/>
-      <c r="B21" s="21"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
-      <c r="G21" s="7"/>
-    </row>
-    <row r="22" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="6"/>
-      <c r="B22" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="6"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" s="16" t="s">
+      <c r="B19" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="C19" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="E19" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="F19" s="17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="28">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="26">
         <v>1</v>
+      </c>
+      <c r="B20" s="20">
+        <v>1092026</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="30">
+        <v>3579</v>
+      </c>
+      <c r="F20" s="26">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="26">
+        <v>2</v>
+      </c>
+      <c r="B21" s="20">
+        <v>1092026</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="31">
+        <v>3571</v>
+      </c>
+      <c r="F21" s="26">
+        <v>40</v>
+      </c>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="32"/>
+    </row>
+    <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="26">
+        <v>3</v>
+      </c>
+      <c r="B22" s="20">
+        <v>1092026</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" s="26"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="32"/>
+      <c r="L22" s="32"/>
+      <c r="M22" s="32"/>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="26">
+        <v>4</v>
+      </c>
+      <c r="B23" s="20">
+        <v>1092026</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" s="26"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="32"/>
+      <c r="M23" s="32"/>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="26">
+        <v>5</v>
+      </c>
+      <c r="B24" s="20">
+        <v>1092026</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="26"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="32"/>
+      <c r="M24" s="32"/>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="26">
+        <v>6</v>
       </c>
       <c r="B25" s="20">
         <v>1092026</v>
       </c>
-      <c r="C25" s="30" t="s">
-        <v>25</v>
+      <c r="C25" s="28" t="s">
+        <v>7</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="32">
-        <v>3579</v>
-      </c>
-      <c r="F25" s="28">
+        <v>36</v>
+      </c>
+      <c r="E25" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" s="26"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="32"/>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="26">
+        <v>7</v>
+      </c>
+      <c r="B26" s="20">
+        <v>1092026</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F26" s="26"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="32"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="26">
+        <v>8</v>
+      </c>
+      <c r="B27" s="20">
+        <v>1092026</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="E27" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F27" s="26"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="26">
+        <v>9</v>
+      </c>
+      <c r="B28" s="20">
+        <v>1092026</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" s="26"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="26">
+        <v>10</v>
+      </c>
+      <c r="B29" s="20">
+        <v>1092026</v>
+      </c>
+      <c r="C29" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="D29" s="35" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="28">
-        <v>2</v>
-      </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="28"/>
-      <c r="I26" s="34"/>
-      <c r="J26" s="34"/>
-      <c r="K26" s="34"/>
-      <c r="L26" s="34"/>
-      <c r="M26" s="34"/>
-    </row>
-    <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="28">
-        <v>3</v>
-      </c>
-      <c r="B27" s="20"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="28"/>
-      <c r="I27" s="34"/>
-      <c r="J27" s="34"/>
-      <c r="K27" s="34"/>
-      <c r="L27" s="34"/>
-      <c r="M27" s="34"/>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="28">
-        <v>4</v>
-      </c>
-      <c r="B28" s="20"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="28"/>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="28">
-        <v>5</v>
-      </c>
-      <c r="B29" s="20"/>
-      <c r="C29" s="36"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="28"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="28">
-        <v>6</v>
+      <c r="E29" s="31">
+        <v>3572</v>
+      </c>
+      <c r="F29" s="26">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="26">
+        <v>11</v>
       </c>
       <c r="B30" s="20"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="28"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="47"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="26"/>
     </row>
     <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="38"/>
-      <c r="B31" s="39"/>
-      <c r="C31" s="40"/>
+      <c r="A31" s="36"/>
+      <c r="B31" s="37"/>
+      <c r="C31" s="38"/>
       <c r="D31"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="38"/>
-    </row>
-    <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="38"/>
-      <c r="B32" s="39"/>
-      <c r="C32" s="40"/>
-      <c r="D32"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="38"/>
-    </row>
-    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E31" s="39"/>
+      <c r="F31" s="36"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
-      <c r="B33" s="12" t="s">
-        <v>20</v>
-      </c>
+      <c r="B33" s="14"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
     </row>
-    <row r="34" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="6"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="15" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B35" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C35" s="16" t="s">
+      <c r="B34" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E35" s="16" t="s">
+      <c r="D34" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="F35" s="17" t="s">
+      <c r="E34" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="F34" s="17" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="26">
+        <v>1</v>
+      </c>
+      <c r="B35" s="20"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+    </row>
     <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="28">
-        <v>1</v>
+      <c r="A36" s="26">
+        <v>2</v>
       </c>
       <c r="B36" s="20"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
+      <c r="C36" s="35"/>
+      <c r="D36" s="35"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="40"/>
     </row>
     <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="28">
-        <v>2</v>
+      <c r="A37" s="26">
+        <v>3</v>
       </c>
       <c r="B37" s="20"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="37"/>
-      <c r="E37" s="42"/>
-      <c r="F37" s="42"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
     </row>
     <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="28">
-        <v>3</v>
+      <c r="A38" s="26">
+        <v>4</v>
       </c>
       <c r="B38" s="20"/>
-      <c r="C38" s="32"/>
-      <c r="D38" s="32"/>
-      <c r="E38" s="42"/>
-      <c r="F38" s="42"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="40"/>
+      <c r="F38" s="40"/>
     </row>
     <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="28">
-        <v>4</v>
+      <c r="A39" s="26">
+        <v>5</v>
       </c>
       <c r="B39" s="20"/>
-      <c r="C39" s="32"/>
-      <c r="D39" s="32"/>
-      <c r="E39" s="42"/>
-      <c r="F39" s="42"/>
-    </row>
-    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="28">
-        <v>5</v>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="41">
+        <v>6</v>
       </c>
       <c r="B40" s="20"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="42"/>
-      <c r="F40" s="42"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="33"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="43">
-        <v>6</v>
+      <c r="A41" s="41">
+        <v>7</v>
       </c>
       <c r="B41" s="20"/>
-      <c r="C41" s="28"/>
-      <c r="D41" s="35"/>
-      <c r="E41" s="32"/>
-      <c r="F41" s="32"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="26"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="43">
-        <v>7</v>
-      </c>
-      <c r="B42" s="20"/>
-      <c r="C42" s="32"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="32"/>
-      <c r="F42" s="28"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F43" s="44"/>
+      <c r="F42" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A3:H3"/>
   </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F42 F20:F21" xr:uid="{8D5CED29-C3B3-4840-830F-0E19160AE997}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F41 F16" xr:uid="{8D5CED29-C3B3-4840-830F-0E19160AE997}">
       <formula1>"20,40,45,50"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F19" xr:uid="{EB3D4CBD-BBEF-4A47-B1AA-9DF877D833AD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F15" xr:uid="{EB3D4CBD-BBEF-4A47-B1AA-9DF877D833AD}">
       <formula1>"20,40,45,50"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1694,9 +1929,562 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74EC856B-C7FE-4404-9D75-FE95EF21C2E2}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="22" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="22" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="22" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="22" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="22"/>
+    <col min="11" max="11" width="14.7109375" style="22" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C15,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B20:B29,"&lt;&gt;",C20:C29,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C20:C29)-F2</f>
+        <v>2</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E20:E29,"VIDE")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="13">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="14"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="18">
+        <v>1</v>
+      </c>
+      <c r="B8" s="49" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="48">
+        <v>2092026</v>
+      </c>
+      <c r="D8" s="50" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="21"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="18">
+        <v>2</v>
+      </c>
+      <c r="B9" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="48">
+        <v>2092026</v>
+      </c>
+      <c r="D9" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="52" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="21"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="18">
+        <v>3</v>
+      </c>
+      <c r="B10" s="43"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="21"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="18">
+        <v>4</v>
+      </c>
+      <c r="B11" s="43"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="21"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="18">
+        <v>5</v>
+      </c>
+      <c r="B12" s="43"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="21"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="18">
+        <v>6</v>
+      </c>
+      <c r="B13" s="43"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="21"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="18">
+        <v>7</v>
+      </c>
+      <c r="B14" s="43"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="21"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="18">
+        <v>8</v>
+      </c>
+      <c r="B15" s="43"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="21"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="6"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="26">
+        <v>1</v>
+      </c>
+      <c r="B20" s="20">
+        <v>2092026</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" s="26">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="26">
+        <v>2</v>
+      </c>
+      <c r="B21" s="20">
+        <v>2092026</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="26">
+        <v>40</v>
+      </c>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="32"/>
+    </row>
+    <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="26">
+        <v>3</v>
+      </c>
+      <c r="B22" s="20"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="26"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="32"/>
+      <c r="L22" s="32"/>
+      <c r="M22" s="32"/>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="26">
+        <v>4</v>
+      </c>
+      <c r="B23" s="20"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="26"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="32"/>
+      <c r="M23" s="32"/>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="26">
+        <v>5</v>
+      </c>
+      <c r="B24" s="20"/>
+      <c r="C24" s="28"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="26"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="32"/>
+      <c r="M24" s="32"/>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="26">
+        <v>6</v>
+      </c>
+      <c r="B25" s="20"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="26"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="32"/>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="26">
+        <v>7</v>
+      </c>
+      <c r="B26" s="20"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="26"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="32"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="26">
+        <v>8</v>
+      </c>
+      <c r="B27" s="20"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="26"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="26">
+        <v>9</v>
+      </c>
+      <c r="B28" s="20"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="26"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="26">
+        <v>10</v>
+      </c>
+      <c r="B29" s="20"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="26"/>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="26">
+        <v>11</v>
+      </c>
+      <c r="B30" s="20"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="47"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="26"/>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="36"/>
+      <c r="B31" s="37"/>
+      <c r="C31" s="38"/>
+      <c r="D31"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="36"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="6"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="F34" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="26">
+        <v>1</v>
+      </c>
+      <c r="B35" s="20">
+        <v>2092026</v>
+      </c>
+      <c r="C35" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="E35" s="40">
+        <v>3575</v>
+      </c>
+      <c r="F35" s="40">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="26">
+        <v>2</v>
+      </c>
+      <c r="B36" s="20">
+        <v>2092026</v>
+      </c>
+      <c r="C36" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="D36" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="E36" s="40">
+        <v>3576</v>
+      </c>
+      <c r="F36" s="40">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="26">
+        <v>3</v>
+      </c>
+      <c r="B37" s="20"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="26">
+        <v>4</v>
+      </c>
+      <c r="B38" s="20"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="40"/>
+      <c r="F38" s="40"/>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="26">
+        <v>5</v>
+      </c>
+      <c r="B39" s="20"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="41">
+        <v>6</v>
+      </c>
+      <c r="B40" s="20"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="33"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="41">
+        <v>7</v>
+      </c>
+      <c r="B41" s="20"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="26"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F42" s="42"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F15" xr:uid="{8BBACC69-AE68-4940-9EE9-D3253579B367}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F41 F16" xr:uid="{D2505F38-AE05-4E92-861B-69325FDB849A}">
+      <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Fiche de mouvement _09-2026.xlsx
+++ b/Fiche de mouvement _09-2026.xlsx
@@ -8,14 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\OneDrive\Documents\Samir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305CBC8F-328A-4A8E-85A0-DA49C8604CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA5E98C9-6021-4B7B-A609-000B354B337A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
   </bookViews>
   <sheets>
     <sheet name="DASHBOARD" sheetId="1" r:id="rId1"/>
     <sheet name="01-09" sheetId="2" r:id="rId2"/>
     <sheet name="02-09" sheetId="3" r:id="rId3"/>
+    <sheet name="03-09" sheetId="4" r:id="rId4"/>
+    <sheet name="06-09" sheetId="5" r:id="rId5"/>
+    <sheet name="07-09" sheetId="6" r:id="rId6"/>
+    <sheet name="08-09" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="94">
   <si>
     <t>Date</t>
   </si>
@@ -98,6 +102,12 @@
     <t>20</t>
   </si>
   <si>
+    <t>CAIU873171 /8</t>
+  </si>
+  <si>
+    <t>MEDU733219 /1</t>
+  </si>
+  <si>
     <t>SORTIE</t>
   </si>
   <si>
@@ -210,6 +220,114 @@
   </si>
   <si>
     <t>LG00557480</t>
+  </si>
+  <si>
+    <t>FBIU026728 /0</t>
+  </si>
+  <si>
+    <t>FX48618480</t>
+  </si>
+  <si>
+    <t>MSMU769241 /6</t>
+  </si>
+  <si>
+    <t>FX48648827</t>
+  </si>
+  <si>
+    <t>0156ICS0112</t>
+  </si>
+  <si>
+    <t>00563-510-31</t>
+  </si>
+  <si>
+    <t>MSMU924819 /1</t>
+  </si>
+  <si>
+    <t>02148-588-31</t>
+  </si>
+  <si>
+    <t>02197-585-31</t>
+  </si>
+  <si>
+    <t>TIIU809713 /9</t>
+  </si>
+  <si>
+    <t>M1726190</t>
+  </si>
+  <si>
+    <t>DRYU455945 /3</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>0754ICS0033</t>
+  </si>
+  <si>
+    <t>0754ICS0069</t>
+  </si>
+  <si>
+    <t>HGTU261674 /4</t>
+  </si>
+  <si>
+    <t>184912</t>
+  </si>
+  <si>
+    <t>TANK</t>
+  </si>
+  <si>
+    <t>0754ICS0106</t>
+  </si>
+  <si>
+    <t>ANNULL</t>
+  </si>
+  <si>
+    <t>MEDU744845 /3</t>
+  </si>
+  <si>
+    <t>006533-508-31</t>
+  </si>
+  <si>
+    <t>CMAU225333 /7</t>
+  </si>
+  <si>
+    <t>00168</t>
+  </si>
+  <si>
+    <t>CMAU265891 /0</t>
+  </si>
+  <si>
+    <t>00183</t>
+  </si>
+  <si>
+    <t>CMAU326542 /0</t>
+  </si>
+  <si>
+    <t>001577</t>
+  </si>
+  <si>
+    <t>SEKU160562 /2</t>
+  </si>
+  <si>
+    <t>00163</t>
+  </si>
+  <si>
+    <t>TCLU734251 /2</t>
+  </si>
+  <si>
+    <t>005369</t>
+  </si>
+  <si>
+    <t>TLLU313561 /8</t>
+  </si>
+  <si>
+    <t>005370</t>
+  </si>
+  <si>
+    <t>00121-517-31</t>
+  </si>
+  <si>
+    <t>00124-517-31</t>
   </si>
 </sst>
 </file>
@@ -218,9 +336,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="166" formatCode="##&quot;/&quot;##&quot;/&quot;####"/>
+    <numFmt numFmtId="165" formatCode="##&quot;/&quot;##&quot;/&quot;####"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -319,6 +437,32 @@
       <sz val="10"/>
       <color rgb="FF334155"/>
       <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -466,7 +610,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -498,9 +642,6 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -523,7 +664,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -574,7 +715,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -605,7 +746,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -619,6 +760,33 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -642,15 +810,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>180975</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>3</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>752475</xdr:colOff>
+      <xdr:colOff>933450</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>209551</xdr:rowOff>
+      <xdr:rowOff>95247</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -679,8 +847,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="3"/>
-          <a:ext cx="2000250" cy="476248"/>
+          <a:off x="180975" y="0"/>
+          <a:ext cx="2000250" cy="495297"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -705,7 +873,7 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>752475</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -735,7 +903,227 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="3"/>
-          <a:ext cx="2000250" cy="523872"/>
+          <a:ext cx="2000250" cy="485772"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>142872</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16AD9580-2333-433B-9112-1D778915CFE4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2000250" cy="542922"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>3</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBC811C5-8BD0-4D50-90C9-361BDEF2E746}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3"/>
+          <a:ext cx="2000250" cy="457197"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>3</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF6463E0-D715-4FF7-8BE6-CD00B622D7F1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3"/>
+          <a:ext cx="2000250" cy="457197"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>3</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89A74B33-2C1E-4DA3-A901-6884EF7E6592}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3"/>
+          <a:ext cx="2000250" cy="476247"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1062,6 +1450,36 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{8104B694-3CF0-4236-B0D3-C3AB4D8B016D}">
+  <we:reference id="wa200007447" version="1.1.6.7" store="fr-FR" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="wa200007447" version="1.1.6.7" store="wa200007447" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
+      <we:customFunctionIdList>
+        <we:customFunctionIds>_xldudf_BOARDFLARE_EXEC</we:customFunctionIds>
+      </we:customFunctionIdList>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B30A621F-D49D-46BA-BFA7-25906CD018F1}">
   <dimension ref="A1:F24"/>
@@ -1106,7 +1524,7 @@
         <v>3</v>
       </c>
       <c r="D2" s="4">
-        <f t="shared" ref="D2:D22" si="0">SUM(B2:C2)</f>
+        <f t="shared" ref="D2" si="0">SUM(B2:C2)</f>
         <v>4</v>
       </c>
       <c r="F2" s="3"/>
@@ -1133,32 +1551,59 @@
       <c r="A4" s="2">
         <v>46268</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="4"/>
+      <c r="B4" s="3">
+        <f>'03-09'!J1</f>
+        <v>2</v>
+      </c>
+      <c r="C4" s="3">
+        <f>'03-09'!J2</f>
+        <v>3</v>
+      </c>
+      <c r="D4" s="4">
+        <f t="shared" ref="D4:D5" si="2">SUM(B4:C4)</f>
+        <v>5</v>
+      </c>
       <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>46269</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="4"/>
+        <v>46271</v>
+      </c>
+      <c r="B5" s="3">
+        <f>'06-09'!H1</f>
+        <v>1</v>
+      </c>
+      <c r="C5" s="3">
+        <f>'06-09'!H2</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>46270</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="4"/>
+        <v>46272</v>
+      </c>
+      <c r="B6" s="3">
+        <f>'07-09'!H1</f>
+        <v>1</v>
+      </c>
+      <c r="C6" s="3">
+        <f>'07-09'!H2</f>
+        <v>7</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" ref="D6" si="3">SUM(B6:C6)</f>
+        <v>8</v>
+      </c>
       <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>46271</v>
+        <v>46273</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -1167,7 +1612,7 @@
     </row>
     <row r="8" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1176,7 +1621,7 @@
     </row>
     <row r="9" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -1309,15 +1754,15 @@
       </c>
       <c r="B24" s="5">
         <f>SUM(B2:B22)</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C24" s="5">
         <f>SUM(C2:C22)</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D24" s="5">
         <f>SUM(D2:D22)</f>
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -1333,16 +1778,16 @@
   <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.140625" style="22" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" style="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" style="22" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" style="22" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="22" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" style="22" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" style="22" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="11.42578125" style="22"/>
-    <col min="11" max="11" width="14.7109375" style="22" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="11.42578125" style="22"/>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -1377,536 +1822,550 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
     </row>
     <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="12">
         <v>46266</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
-      <c r="B6" s="14"/>
+      <c r="B6" s="13"/>
     </row>
     <row r="7" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="16" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="18">
+      <c r="A8" s="17">
         <v>1</v>
       </c>
-      <c r="B8" s="46" t="s">
+      <c r="B8" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="19">
+        <v>1092026</v>
+      </c>
+      <c r="D8" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="20">
-        <v>1092026</v>
-      </c>
-      <c r="D8" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="44" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="45" t="s">
+      <c r="E8" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="21"/>
+      <c r="G8" s="20"/>
     </row>
     <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="18">
+      <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="43"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="21"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="20"/>
     </row>
     <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="18">
+      <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="43"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="21"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="20"/>
     </row>
     <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="18">
+      <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="43"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="21"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="20"/>
     </row>
     <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="18">
+      <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="21"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="20"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="18">
+      <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="43"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="21"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="20"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="18">
+      <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="21"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="20"/>
     </row>
     <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="18">
+      <c r="A15" s="17">
         <v>8</v>
       </c>
-      <c r="B15" s="43"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="21"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="20"/>
     </row>
     <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
-      <c r="B16" s="21"/>
+      <c r="B16" s="20"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
-      <c r="B17" s="12" t="s">
-        <v>18</v>
+      <c r="B17" s="11" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
-      <c r="B18" s="14"/>
+      <c r="B18" s="13"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="16" t="s">
+      <c r="B19" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="17" t="s">
+      <c r="F19" s="16" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="26">
+      <c r="A20" s="25">
         <v>1</v>
       </c>
-      <c r="B20" s="20">
+      <c r="B20" s="19">
         <v>1092026</v>
       </c>
-      <c r="C20" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="30">
+      <c r="C20" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="29">
         <v>3579</v>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="25">
         <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="26">
+      <c r="A21" s="25">
         <v>2</v>
       </c>
-      <c r="B21" s="20">
+      <c r="B21" s="19">
         <v>1092026</v>
       </c>
-      <c r="C21" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="E21" s="31">
+      <c r="C21" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="30">
         <v>3571</v>
       </c>
-      <c r="F21" s="26">
+      <c r="F21" s="25">
         <v>40</v>
       </c>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
-      <c r="L21" s="32"/>
-      <c r="M21" s="32"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="31"/>
     </row>
     <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="26">
+      <c r="A22" s="25">
         <v>3</v>
       </c>
-      <c r="B22" s="20">
+      <c r="B22" s="19">
         <v>1092026</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="C22" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D22" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="F22" s="26"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
-      <c r="L22" s="32"/>
-      <c r="M22" s="32"/>
+      <c r="D22" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="F22" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
     </row>
     <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="26">
+      <c r="A23" s="25">
         <v>4</v>
       </c>
-      <c r="B23" s="20">
+      <c r="B23" s="19">
         <v>1092026</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D23" s="31" t="s">
+      <c r="D23" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="E23" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="F23" s="26"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
-      <c r="L23" s="32"/>
-      <c r="M23" s="32"/>
+      <c r="F23" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
     </row>
     <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="26">
+      <c r="A24" s="25">
         <v>5</v>
       </c>
-      <c r="B24" s="20">
+      <c r="B24" s="19">
         <v>1092026</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D24" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="E24" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" s="26"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="32"/>
-      <c r="K24" s="32"/>
-      <c r="L24" s="32"/>
-      <c r="M24" s="32"/>
+      <c r="D24" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="F24" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
     </row>
     <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="26">
+      <c r="A25" s="25">
         <v>6</v>
       </c>
-      <c r="B25" s="20">
+      <c r="B25" s="19">
         <v>1092026</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="E25" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="F25" s="26"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32"/>
-      <c r="L25" s="32"/>
-      <c r="M25" s="32"/>
+      <c r="D25" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="F25" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
     </row>
     <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="26">
+      <c r="A26" s="25">
         <v>7</v>
       </c>
-      <c r="B26" s="20">
+      <c r="B26" s="19">
         <v>1092026</v>
       </c>
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="E26" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="F26" s="26"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="32"/>
-      <c r="L26" s="32"/>
-      <c r="M26" s="32"/>
+      <c r="D26" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="F26" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="26">
+      <c r="A27" s="25">
         <v>8</v>
       </c>
-      <c r="B27" s="20">
+      <c r="B27" s="19">
         <v>1092026</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D27" s="35" t="s">
-        <v>38</v>
-      </c>
-      <c r="E27" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="F27" s="26"/>
+      <c r="D27" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="F27" s="27" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="26">
+      <c r="A28" s="25">
         <v>9</v>
       </c>
-      <c r="B28" s="20">
+      <c r="B28" s="19">
         <v>1092026</v>
       </c>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D28" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="E28" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="F28" s="26"/>
+      <c r="D28" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="E28" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="F28" s="27" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="26">
+      <c r="A29" s="25">
         <v>10</v>
       </c>
-      <c r="B29" s="20">
+      <c r="B29" s="19">
         <v>1092026</v>
       </c>
-      <c r="C29" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="D29" s="35" t="s">
+      <c r="C29" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" s="30">
+        <v>3572</v>
+      </c>
+      <c r="F29" s="25">
         <v>40</v>
       </c>
-      <c r="E29" s="31">
-        <v>3572</v>
-      </c>
-      <c r="F29" s="26">
-        <v>40</v>
-      </c>
     </row>
     <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="26">
+      <c r="A30" s="25">
         <v>11</v>
       </c>
-      <c r="B30" s="20"/>
-      <c r="C30" s="34"/>
-      <c r="D30" s="47"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="26"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="25"/>
     </row>
     <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="36"/>
-      <c r="B31" s="37"/>
-      <c r="C31" s="38"/>
+      <c r="A31" s="35"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="37"/>
       <c r="D31"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="36"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="35"/>
     </row>
     <row r="32" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="6"/>
-      <c r="B32" s="12" t="s">
-        <v>21</v>
+      <c r="B32" s="11" t="s">
+        <v>23</v>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
     </row>
     <row r="33" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
-      <c r="B33" s="14"/>
+      <c r="B33" s="13"/>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B34" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C34" s="16" t="s">
+      <c r="B34" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E34" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="F34" s="17" t="s">
+      <c r="D34" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F34" s="16" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="26">
+      <c r="A35" s="25">
         <v>1</v>
       </c>
-      <c r="B35" s="20"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="40"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="39"/>
     </row>
     <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="26">
+      <c r="A36" s="25">
         <v>2</v>
       </c>
-      <c r="B36" s="20"/>
-      <c r="C36" s="35"/>
-      <c r="D36" s="35"/>
-      <c r="E36" s="40"/>
-      <c r="F36" s="40"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="34"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
     </row>
     <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="26">
+      <c r="A37" s="25">
         <v>3</v>
       </c>
-      <c r="B37" s="20"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="40"/>
-      <c r="F37" s="40"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
     </row>
     <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="26">
+      <c r="A38" s="25">
         <v>4</v>
       </c>
-      <c r="B38" s="20"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="40"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
     </row>
     <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="26">
+      <c r="A39" s="25">
         <v>5</v>
       </c>
-      <c r="B39" s="20"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="40"/>
-      <c r="F39" s="40"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="41">
+      <c r="A40" s="40">
         <v>6</v>
       </c>
-      <c r="B40" s="20"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="33"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="41">
+      <c r="A41" s="40">
         <v>7</v>
       </c>
-      <c r="B41" s="20"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="26"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="25"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F42" s="42"/>
+      <c r="F42" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1922,8 +2381,9 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1932,16 +2392,16 @@
   <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.140625" style="22" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" style="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" style="22" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" style="22" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="22" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" style="22" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" style="22" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="11.42578125" style="22"/>
-    <col min="11" max="11" width="14.7109375" style="22" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="11.42578125" style="22"/>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -1976,500 +2436,500 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
     </row>
     <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="13">
-        <v>46266</v>
+      <c r="G5" s="12">
+        <v>46267</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
-      <c r="B6" s="14"/>
+      <c r="B6" s="13"/>
     </row>
     <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="16" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="18">
+      <c r="A8" s="17">
         <v>1</v>
       </c>
-      <c r="B8" s="49" t="s">
+      <c r="B8" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="47">
+        <v>2092026</v>
+      </c>
+      <c r="D8" s="49" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="20"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>2</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="47">
+        <v>2092026</v>
+      </c>
+      <c r="D9" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="48">
-        <v>2092026</v>
-      </c>
-      <c r="D8" s="50" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" s="50" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="19" t="s">
+      <c r="E9" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="21"/>
-    </row>
-    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="18">
-        <v>2</v>
-      </c>
-      <c r="B9" s="51" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" s="48">
-        <v>2092026</v>
-      </c>
-      <c r="D9" s="52" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="52" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="21"/>
+      <c r="G9" s="20"/>
     </row>
     <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="18">
+      <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="43"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="21"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="20"/>
     </row>
     <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="18">
+      <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="43"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="21"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="20"/>
     </row>
     <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="18">
+      <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="21"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="20"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="18">
+      <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="43"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="21"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="20"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="18">
+      <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="21"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="20"/>
     </row>
     <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="18">
+      <c r="A15" s="17">
         <v>8</v>
       </c>
-      <c r="B15" s="43"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="21"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="20"/>
     </row>
     <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
-      <c r="B16" s="21"/>
+      <c r="B16" s="20"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
-      <c r="B17" s="12" t="s">
-        <v>18</v>
+      <c r="B17" s="11" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
-      <c r="B18" s="14"/>
+      <c r="B18" s="13"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="16" t="s">
+      <c r="B19" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="17" t="s">
+      <c r="F19" s="16" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="26">
+      <c r="A20" s="25">
         <v>1</v>
       </c>
-      <c r="B20" s="20">
+      <c r="B20" s="19">
         <v>2092026</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="E20" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="F20" s="26">
+      <c r="E20" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="25">
         <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="26">
+      <c r="A21" s="25">
         <v>2</v>
       </c>
-      <c r="B21" s="20">
+      <c r="B21" s="19">
         <v>2092026</v>
       </c>
-      <c r="C21" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="D21" s="31" t="s">
+      <c r="C21" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="E21" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="F21" s="26">
+      <c r="F21" s="25">
         <v>40</v>
       </c>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
-      <c r="L21" s="32"/>
-      <c r="M21" s="32"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="31"/>
     </row>
     <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="26">
+      <c r="A22" s="25">
         <v>3</v>
       </c>
-      <c r="B22" s="20"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="26"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
-      <c r="L22" s="32"/>
-      <c r="M22" s="32"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="25"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
     </row>
     <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="26">
+      <c r="A23" s="25">
         <v>4</v>
       </c>
-      <c r="B23" s="20"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="26"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
-      <c r="L23" s="32"/>
-      <c r="M23" s="32"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="25"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
     </row>
     <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="26">
+      <c r="A24" s="25">
         <v>5</v>
       </c>
-      <c r="B24" s="20"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="26"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="32"/>
-      <c r="K24" s="32"/>
-      <c r="L24" s="32"/>
-      <c r="M24" s="32"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="25"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
     </row>
     <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="26">
+      <c r="A25" s="25">
         <v>6</v>
       </c>
-      <c r="B25" s="20"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="26"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32"/>
-      <c r="L25" s="32"/>
-      <c r="M25" s="32"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="25"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
     </row>
     <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="26">
+      <c r="A26" s="25">
         <v>7</v>
       </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="26"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="32"/>
-      <c r="L26" s="32"/>
-      <c r="M26" s="32"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="25"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="26">
+      <c r="A27" s="25">
         <v>8</v>
       </c>
-      <c r="B27" s="20"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="26"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="25"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="26">
+      <c r="A28" s="25">
         <v>9</v>
       </c>
-      <c r="B28" s="20"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="26"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="25"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="26">
+      <c r="A29" s="25">
         <v>10</v>
       </c>
-      <c r="B29" s="20"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="26"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="25"/>
     </row>
     <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="26">
+      <c r="A30" s="25">
         <v>11</v>
       </c>
-      <c r="B30" s="20"/>
-      <c r="C30" s="34"/>
-      <c r="D30" s="47"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="26"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="25"/>
     </row>
     <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="36"/>
-      <c r="B31" s="37"/>
-      <c r="C31" s="38"/>
+      <c r="A31" s="35"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="37"/>
       <c r="D31"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="36"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="35"/>
     </row>
     <row r="32" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="6"/>
-      <c r="B32" s="12" t="s">
-        <v>21</v>
+      <c r="B32" s="11" t="s">
+        <v>23</v>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
     </row>
     <row r="33" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
-      <c r="B33" s="14"/>
+      <c r="B33" s="13"/>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B34" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C34" s="16" t="s">
+      <c r="B34" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E34" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="F34" s="17" t="s">
+      <c r="D34" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F34" s="16" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="26">
+      <c r="A35" s="25">
         <v>1</v>
       </c>
-      <c r="B35" s="20">
+      <c r="B35" s="19">
         <v>2092026</v>
       </c>
-      <c r="C35" s="35" t="s">
-        <v>52</v>
-      </c>
-      <c r="D35" s="35" t="s">
+      <c r="C35" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="E35" s="40">
+      <c r="D35" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="E35" s="39">
         <v>3575</v>
       </c>
-      <c r="F35" s="40">
+      <c r="F35" s="39">
         <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="26">
+      <c r="A36" s="25">
         <v>2</v>
       </c>
-      <c r="B36" s="20">
+      <c r="B36" s="19">
         <v>2092026</v>
       </c>
-      <c r="C36" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="D36" s="35" t="s">
+      <c r="C36" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="E36" s="40">
+      <c r="D36" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="E36" s="39">
         <v>3576</v>
       </c>
-      <c r="F36" s="40">
+      <c r="F36" s="39">
         <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="26">
+      <c r="A37" s="25">
         <v>3</v>
       </c>
-      <c r="B37" s="20"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="40"/>
-      <c r="F37" s="40"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
     </row>
     <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="26">
+      <c r="A38" s="25">
         <v>4</v>
       </c>
-      <c r="B38" s="20"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="40"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
     </row>
     <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="26">
+      <c r="A39" s="25">
         <v>5</v>
       </c>
-      <c r="B39" s="20"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="40"/>
-      <c r="F39" s="40"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="41">
+      <c r="A40" s="40">
         <v>6</v>
       </c>
-      <c r="B40" s="20"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="33"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="41">
+      <c r="A41" s="40">
         <v>7</v>
       </c>
-      <c r="B41" s="20"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="26"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="25"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F42" s="42"/>
+      <c r="F42" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2484,6 +2944,2168 @@
       <formula1>"20,40,45,50"</formula1>
     </dataValidation>
   </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{340190F6-620A-405F-A592-028D59F85BE0}">
+  <dimension ref="A1:M42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="J1" s="8">
+        <f>COUNTIF(C8:C15,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="H2" s="8">
+        <f>COUNTIFS(B20:B29,"&lt;&gt;",C20:C29,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="8">
+        <f>COUNTA(C20:C29)-H2</f>
+        <v>3</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="10">
+        <f>COUNTIF(E20:E29,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="52" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+    </row>
+    <row r="4" spans="1:12" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46268</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:12" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>1</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="47">
+        <v>3092026</v>
+      </c>
+      <c r="D8" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="20"/>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>2</v>
+      </c>
+      <c r="B9" s="54" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="47">
+        <v>3092026</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>3</v>
+      </c>
+      <c r="B10" s="42"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>4</v>
+      </c>
+      <c r="B11" s="42"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="20"/>
+    </row>
+    <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>5</v>
+      </c>
+      <c r="B12" s="42"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>6</v>
+      </c>
+      <c r="B13" s="42"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
+        <v>7</v>
+      </c>
+      <c r="B14" s="42"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="20"/>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
+        <v>8</v>
+      </c>
+      <c r="B15" s="42"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="6"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="25">
+        <v>1</v>
+      </c>
+      <c r="B20" s="19">
+        <v>3092026</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" s="29">
+        <v>3578</v>
+      </c>
+      <c r="F20" s="25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="25">
+        <v>2</v>
+      </c>
+      <c r="B21" s="19">
+        <v>3092026</v>
+      </c>
+      <c r="C21" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="39">
+        <v>3573</v>
+      </c>
+      <c r="F21" s="25">
+        <v>40</v>
+      </c>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="31"/>
+    </row>
+    <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="25">
+        <v>3</v>
+      </c>
+      <c r="B22" s="19">
+        <v>3092026</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="39">
+        <v>3574</v>
+      </c>
+      <c r="F22" s="25">
+        <v>40</v>
+      </c>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="25">
+        <v>4</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="25"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="25">
+        <v>5</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="25"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="25">
+        <v>6</v>
+      </c>
+      <c r="B25" s="19"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="25"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="25">
+        <v>7</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="25"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="25">
+        <v>8</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="25"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="25">
+        <v>9</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="25"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="25">
+        <v>10</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="25"/>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="25">
+        <v>11</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="25"/>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="35"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="37"/>
+      <c r="D31"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="35"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="6"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="25">
+        <v>1</v>
+      </c>
+      <c r="B35" s="19"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="39"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="25">
+        <v>2</v>
+      </c>
+      <c r="B36" s="19"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="25">
+        <v>3</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="25">
+        <v>4</v>
+      </c>
+      <c r="B38" s="19"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="25">
+        <v>5</v>
+      </c>
+      <c r="B39" s="19"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="40">
+        <v>6</v>
+      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="40">
+        <v>7</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="25"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F42" s="41"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F41 F16" xr:uid="{B1F619BD-3EA3-41B1-A495-D1424868D8F1}">
+      <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F15" xr:uid="{B8E3B6BF-1734-4653-860B-14E738E727DC}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E056CC4-8E30-4C4B-8984-EC96F1E08576}">
+  <dimension ref="A1:M42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C15,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B20:B29,"&lt;&gt;",C20:C29,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C20:C29)-F2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E20:E29,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="52" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46271</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>1</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="19">
+        <v>6092026</v>
+      </c>
+      <c r="D8" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="20"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>2</v>
+      </c>
+      <c r="B9" s="58" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="56" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="55" t="s">
+        <v>77</v>
+      </c>
+      <c r="F9" s="57" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>3</v>
+      </c>
+      <c r="B10" s="42"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>4</v>
+      </c>
+      <c r="B11" s="42"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="20"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>5</v>
+      </c>
+      <c r="B12" s="42"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>6</v>
+      </c>
+      <c r="B13" s="42"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
+        <v>7</v>
+      </c>
+      <c r="B14" s="42"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="20"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
+        <v>8</v>
+      </c>
+      <c r="B15" s="42"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="6"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="25">
+        <v>1</v>
+      </c>
+      <c r="B20" s="19"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="25"/>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="25">
+        <v>2</v>
+      </c>
+      <c r="B21" s="19"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="25"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="31"/>
+    </row>
+    <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="25">
+        <v>3</v>
+      </c>
+      <c r="B22" s="19"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="25"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="25">
+        <v>4</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="25"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="25">
+        <v>5</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="25"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="25">
+        <v>6</v>
+      </c>
+      <c r="B25" s="19"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="25"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="25">
+        <v>7</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="25"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="25">
+        <v>8</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="25"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="25">
+        <v>9</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="25"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="25">
+        <v>10</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="25"/>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="25">
+        <v>11</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="25"/>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="35"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="37"/>
+      <c r="D31"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="35"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="6"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="25">
+        <v>1</v>
+      </c>
+      <c r="B35" s="19"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="39"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="25">
+        <v>2</v>
+      </c>
+      <c r="B36" s="19"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="25">
+        <v>3</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="25">
+        <v>4</v>
+      </c>
+      <c r="B38" s="19"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="25">
+        <v>5</v>
+      </c>
+      <c r="B39" s="19"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="40">
+        <v>6</v>
+      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="40">
+        <v>7</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="25"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F42" s="41"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F15" xr:uid="{49196DC9-871A-49B7-B76F-217BE4312612}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F41 F16" xr:uid="{E6B381A0-C4BE-4983-9414-E5E4F42AD60C}">
+      <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78A58D52-F617-4B72-ADA0-C765A313D71B}">
+  <dimension ref="A1:M42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C15,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B20:B29,"&lt;&gt;",C20:C29,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C20:C29)-F2</f>
+        <v>7</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E20:E29,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="52" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>1</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="19">
+        <v>7092026</v>
+      </c>
+      <c r="D8" s="53" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="53" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" s="18">
+        <v>20</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>2</v>
+      </c>
+      <c r="B9" s="54"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>3</v>
+      </c>
+      <c r="B10" s="42"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>4</v>
+      </c>
+      <c r="B11" s="42"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="20"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>5</v>
+      </c>
+      <c r="B12" s="42"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>6</v>
+      </c>
+      <c r="B13" s="42"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
+        <v>7</v>
+      </c>
+      <c r="B14" s="42"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="20"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
+        <v>8</v>
+      </c>
+      <c r="B15" s="42"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="6"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="25">
+        <v>1</v>
+      </c>
+      <c r="B20" s="19">
+        <v>7092026</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" s="29">
+        <v>3994</v>
+      </c>
+      <c r="F20" s="25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="25">
+        <v>2</v>
+      </c>
+      <c r="B21" s="19">
+        <v>7092026</v>
+      </c>
+      <c r="C21" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21" s="59" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" s="25">
+        <v>20</v>
+      </c>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="31"/>
+    </row>
+    <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="25">
+        <v>3</v>
+      </c>
+      <c r="B22" s="19">
+        <v>7092026</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" s="59" t="s">
+        <v>83</v>
+      </c>
+      <c r="F22" s="25">
+        <v>20</v>
+      </c>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="25">
+        <v>4</v>
+      </c>
+      <c r="B23" s="19">
+        <v>7092026</v>
+      </c>
+      <c r="C23" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="F23" s="25">
+        <v>20</v>
+      </c>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="25">
+        <v>5</v>
+      </c>
+      <c r="B24" s="19">
+        <v>7092026</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24" s="60" t="s">
+        <v>87</v>
+      </c>
+      <c r="F24" s="25">
+        <v>20</v>
+      </c>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="25">
+        <v>6</v>
+      </c>
+      <c r="B25" s="19">
+        <v>7092026</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="E25" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="F25" s="25">
+        <v>20</v>
+      </c>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="25">
+        <v>7</v>
+      </c>
+      <c r="B26" s="19">
+        <v>7092026</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="F26" s="25">
+        <v>20</v>
+      </c>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="25">
+        <v>8</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="25"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="25">
+        <v>9</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="25"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="25">
+        <v>10</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="25"/>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="25">
+        <v>11</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="25"/>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="35"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="37"/>
+      <c r="D31"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="35"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="6"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="25">
+        <v>1</v>
+      </c>
+      <c r="B35" s="19"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="39"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="25">
+        <v>2</v>
+      </c>
+      <c r="B36" s="19"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="25">
+        <v>3</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="25">
+        <v>4</v>
+      </c>
+      <c r="B38" s="19"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="25">
+        <v>5</v>
+      </c>
+      <c r="B39" s="19"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="40">
+        <v>6</v>
+      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="40">
+        <v>7</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="25"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F42" s="41"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F41 F16" xr:uid="{CE340E61-1C9A-4626-AE21-92A800AC9FC7}">
+      <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F15" xr:uid="{11B51B2B-7C69-4E18-85F6-9C40A9E67DBF}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45F11B97-4126-4C83-B74A-4E710002A39D}">
+  <dimension ref="A1:M42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C15,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B20:B29,"&lt;&gt;",C20:C29,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C20:C29)-F2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E20:E29,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="52" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46273</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>1</v>
+      </c>
+      <c r="B8" s="17"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="20"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>2</v>
+      </c>
+      <c r="B9" s="54"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>3</v>
+      </c>
+      <c r="B10" s="42"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>4</v>
+      </c>
+      <c r="B11" s="42"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="20"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>5</v>
+      </c>
+      <c r="B12" s="42"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>6</v>
+      </c>
+      <c r="B13" s="42"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
+        <v>7</v>
+      </c>
+      <c r="B14" s="42"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="20"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
+        <v>8</v>
+      </c>
+      <c r="B15" s="42"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="6"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="25">
+        <v>1</v>
+      </c>
+      <c r="B20" s="19">
+        <v>7092026</v>
+      </c>
+      <c r="C20" s="27"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="25"/>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="25">
+        <v>2</v>
+      </c>
+      <c r="B21" s="19"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="25"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="31"/>
+    </row>
+    <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="25">
+        <v>3</v>
+      </c>
+      <c r="B22" s="19"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="25"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="25">
+        <v>4</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="25"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="25">
+        <v>5</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="60"/>
+      <c r="F24" s="25"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="25">
+        <v>6</v>
+      </c>
+      <c r="B25" s="19"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="25"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="25">
+        <v>7</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="25"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="25">
+        <v>8</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="25"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="25">
+        <v>9</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="25"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="25">
+        <v>10</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="25"/>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="25">
+        <v>11</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="25"/>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="35"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="37"/>
+      <c r="D31"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="35"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="6"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="25">
+        <v>1</v>
+      </c>
+      <c r="B35" s="19"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="39"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="25">
+        <v>2</v>
+      </c>
+      <c r="B36" s="19"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="25">
+        <v>3</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="25">
+        <v>4</v>
+      </c>
+      <c r="B38" s="19"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="25">
+        <v>5</v>
+      </c>
+      <c r="B39" s="19"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="40">
+        <v>6</v>
+      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="40">
+        <v>7</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="25"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F42" s="41"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F15" xr:uid="{2EC0EC5B-7C08-4C22-AA95-368F2D69FED9}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F41 F16" xr:uid="{14D22049-3295-498F-9836-6B814172B93A}">
+      <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Fiche de mouvement _09-2026.xlsx
+++ b/Fiche de mouvement _09-2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\OneDrive\Documents\Samir\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ab0b5a2ed962cae/Documents/Samir/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA5E98C9-6021-4B7B-A609-000B354B337A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E527636B-0A8B-40F1-81C6-614DDE3390C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
   </bookViews>
   <sheets>
     <sheet name="DASHBOARD" sheetId="1" r:id="rId1"/>
@@ -20,8 +20,11 @@
     <sheet name="06-09" sheetId="5" r:id="rId5"/>
     <sheet name="07-09" sheetId="6" r:id="rId6"/>
     <sheet name="08-09" sheetId="7" r:id="rId7"/>
+    <sheet name="09-09" sheetId="8" r:id="rId8"/>
+    <sheet name="10-09" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -45,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="142">
   <si>
     <t>Date</t>
   </si>
@@ -328,6 +331,150 @@
   </si>
   <si>
     <t>00124-517-31</t>
+  </si>
+  <si>
+    <t>CMAU995757 /7</t>
+  </si>
+  <si>
+    <t>M2002559</t>
+  </si>
+  <si>
+    <t>0765ICS0037</t>
+  </si>
+  <si>
+    <t>ECMU753339 /6</t>
+  </si>
+  <si>
+    <t>J1979281</t>
+  </si>
+  <si>
+    <t>0083ICS0038</t>
+  </si>
+  <si>
+    <t>MRSU491361 /6</t>
+  </si>
+  <si>
+    <t>CN6436798</t>
+  </si>
+  <si>
+    <t>0083ICS0014</t>
+  </si>
+  <si>
+    <t>GCXU573668 /2</t>
+  </si>
+  <si>
+    <t>CN6536328</t>
+  </si>
+  <si>
+    <t>0765ICS0233</t>
+  </si>
+  <si>
+    <t>APHU463551 /5</t>
+  </si>
+  <si>
+    <t>M9168709</t>
+  </si>
+  <si>
+    <t>0765ICS0116</t>
+  </si>
+  <si>
+    <t>ECMU814116 /8</t>
+  </si>
+  <si>
+    <t>J0695804</t>
+  </si>
+  <si>
+    <t>0083ICS0144</t>
+  </si>
+  <si>
+    <t>TGHU805347 /3</t>
+  </si>
+  <si>
+    <t>0083ICS0079</t>
+  </si>
+  <si>
+    <t>MRSU215858 /4</t>
+  </si>
+  <si>
+    <t>CN8343648</t>
+  </si>
+  <si>
+    <t>0671ICS0026</t>
+  </si>
+  <si>
+    <t>HDMU321504 /6</t>
+  </si>
+  <si>
+    <t>25H1013125</t>
+  </si>
+  <si>
+    <t>HDMU341436 /7</t>
+  </si>
+  <si>
+    <t>25H1041732</t>
+  </si>
+  <si>
+    <t>HDMU342017 /0</t>
+  </si>
+  <si>
+    <t>25H1175272</t>
+  </si>
+  <si>
+    <t>HDMU342266 /0</t>
+  </si>
+  <si>
+    <t>25H1175275</t>
+  </si>
+  <si>
+    <t>KOCU430655 /1</t>
+  </si>
+  <si>
+    <t>26H0234922</t>
+  </si>
+  <si>
+    <t>TIIU600821 /4</t>
+  </si>
+  <si>
+    <t>26H0236033</t>
+  </si>
+  <si>
+    <t>0159ICS0027</t>
+  </si>
+  <si>
+    <t>FFAU811399 /0</t>
+  </si>
+  <si>
+    <t>18233786</t>
+  </si>
+  <si>
+    <t>0159ICS0010</t>
+  </si>
+  <si>
+    <t>CSNU688630 /2</t>
+  </si>
+  <si>
+    <t>CX185022</t>
+  </si>
+  <si>
+    <t>0159ICS0008</t>
+  </si>
+  <si>
+    <t>ARKU855448 /4</t>
+  </si>
+  <si>
+    <t>239388</t>
+  </si>
+  <si>
+    <t>0159ICS0007</t>
+  </si>
+  <si>
+    <t>ARKU150130 /6</t>
+  </si>
+  <si>
+    <t>1441385</t>
+  </si>
+  <si>
+    <t>Date ACC</t>
   </si>
 </sst>
 </file>
@@ -522,7 +669,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -606,11 +753,63 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -761,9 +960,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -787,6 +983,24 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1124,6 +1338,116 @@
         <a:xfrm>
           <a:off x="0" y="3"/>
           <a:ext cx="2000250" cy="476247"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>3</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34017FB2-1320-404C-99C9-DEEBADD745CE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3"/>
+          <a:ext cx="2000250" cy="419097"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>3</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BA9419C-B4CB-4FFD-B6E5-4C3A714E7753}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3"/>
+          <a:ext cx="2000250" cy="419097"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1524,7 +1848,7 @@
         <v>3</v>
       </c>
       <c r="D2" s="4">
-        <f t="shared" ref="D2" si="0">SUM(B2:C2)</f>
+        <f t="shared" ref="D2:D7" si="0">SUM(B2:C2)</f>
         <v>4</v>
       </c>
       <c r="F2" s="3"/>
@@ -1542,7 +1866,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="4">
-        <f t="shared" ref="D3" si="1">SUM(B3:C3)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="F3" s="3"/>
@@ -1560,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="4">
-        <f t="shared" ref="D4:D5" si="2">SUM(B4:C4)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="F4" s="3"/>
@@ -1578,7 +1902,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="F5" s="3"/>
@@ -1596,7 +1920,7 @@
         <v>7</v>
       </c>
       <c r="D6" s="4">
-        <f t="shared" ref="D6" si="3">SUM(B6:C6)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="F6" s="3"/>
@@ -1605,27 +1929,54 @@
       <c r="A7" s="2">
         <v>46273</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="4"/>
+      <c r="B7" s="3">
+        <f>'08-09'!H1</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="3">
+        <f>'08-09'!H2</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>46274</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="4"/>
+      <c r="B8" s="3">
+        <f>'09-09'!H1</f>
+        <v>11</v>
+      </c>
+      <c r="C8" s="3">
+        <f>'09-09'!H2</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" ref="D8:D9" si="1">SUM(B8:C8)</f>
+        <v>11</v>
+      </c>
       <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>46275</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="4"/>
+      <c r="B9" s="3">
+        <f>'10-09'!H1</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="3">
+        <f>'10-09'!H2</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -1754,7 +2105,7 @@
       </c>
       <c r="B24" s="5">
         <f>SUM(B2:B22)</f>
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C24" s="5">
         <f>SUM(C2:C22)</f>
@@ -1762,7 +2113,7 @@
       </c>
       <c r="D24" s="5">
         <f>SUM(D2:D22)</f>
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -1822,16 +2173,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -2436,16 +2787,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -2999,16 +3350,16 @@
       </c>
     </row>
     <row r="3" spans="1:12" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
     </row>
     <row r="4" spans="1:12" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -3056,10 +3407,10 @@
       <c r="C8" s="47">
         <v>3092026</v>
       </c>
-      <c r="D8" s="53" t="s">
+      <c r="D8" s="52" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="53" t="s">
+      <c r="E8" s="52" t="s">
         <v>59</v>
       </c>
       <c r="F8" s="18" t="s">
@@ -3071,7 +3422,7 @@
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="53" t="s">
         <v>62</v>
       </c>
       <c r="C9" s="47">
@@ -3552,16 +3903,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -3609,10 +3960,10 @@
       <c r="C8" s="19">
         <v>6092026</v>
       </c>
-      <c r="D8" s="53" t="s">
+      <c r="D8" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="E8" s="53" t="s">
+      <c r="E8" s="52" t="s">
         <v>68</v>
       </c>
       <c r="F8" s="18" t="s">
@@ -3624,16 +3975,16 @@
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="58" t="s">
+      <c r="B9" s="57" t="s">
         <v>72</v>
       </c>
-      <c r="D9" s="56" t="s">
+      <c r="D9" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="55" t="s">
+      <c r="E9" s="54" t="s">
         <v>77</v>
       </c>
-      <c r="F9" s="57" t="s">
+      <c r="F9" s="56" t="s">
         <v>70</v>
       </c>
       <c r="G9" s="20"/>
@@ -4072,16 +4423,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -4129,10 +4480,10 @@
       <c r="C8" s="19">
         <v>7092026</v>
       </c>
-      <c r="D8" s="53" t="s">
+      <c r="D8" s="52" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="53" t="s">
+      <c r="E8" s="52" t="s">
         <v>74</v>
       </c>
       <c r="F8" s="18">
@@ -4146,7 +4497,7 @@
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="54"/>
+      <c r="B9" s="53"/>
       <c r="C9" s="47"/>
       <c r="D9" s="22"/>
       <c r="E9" s="18"/>
@@ -4295,7 +4646,7 @@
       <c r="D21" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="E21" s="59" t="s">
+      <c r="E21" s="58" t="s">
         <v>81</v>
       </c>
       <c r="F21" s="25">
@@ -4320,7 +4671,7 @@
       <c r="D22" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="E22" s="59" t="s">
+      <c r="E22" s="58" t="s">
         <v>83</v>
       </c>
       <c r="F22" s="25">
@@ -4370,7 +4721,7 @@
       <c r="D24" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="E24" s="60" t="s">
+      <c r="E24" s="59" t="s">
         <v>87</v>
       </c>
       <c r="F24" s="25">
@@ -4602,8 +4953,9 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -4656,16 +5008,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -4709,8 +5061,8 @@
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="19"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
       <c r="F8" s="18"/>
       <c r="G8" s="20"/>
     </row>
@@ -4718,7 +5070,7 @@
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="54"/>
+      <c r="B9" s="53"/>
       <c r="C9" s="47"/>
       <c r="D9" s="22"/>
       <c r="E9" s="18"/>
@@ -4838,9 +5190,7 @@
       <c r="A20" s="25">
         <v>1</v>
       </c>
-      <c r="B20" s="19">
-        <v>7092026</v>
-      </c>
+      <c r="B20" s="19"/>
       <c r="C20" s="27"/>
       <c r="D20" s="28"/>
       <c r="E20" s="29"/>
@@ -4853,7 +5203,7 @@
       <c r="B21" s="19"/>
       <c r="C21" s="29"/>
       <c r="D21" s="18"/>
-      <c r="E21" s="59"/>
+      <c r="E21" s="58"/>
       <c r="F21" s="25"/>
       <c r="I21" s="31"/>
       <c r="J21" s="31"/>
@@ -4868,7 +5218,7 @@
       <c r="B22" s="19"/>
       <c r="C22" s="27"/>
       <c r="D22" s="18"/>
-      <c r="E22" s="59"/>
+      <c r="E22" s="58"/>
       <c r="F22" s="25"/>
       <c r="I22" s="31"/>
       <c r="J22" s="31"/>
@@ -4898,7 +5248,7 @@
       <c r="B24" s="19"/>
       <c r="C24" s="29"/>
       <c r="D24" s="18"/>
-      <c r="E24" s="60"/>
+      <c r="E24" s="59"/>
       <c r="F24" s="25"/>
       <c r="I24" s="31"/>
       <c r="J24" s="31"/>
@@ -5024,11 +5374,21 @@
       <c r="A35" s="25">
         <v>1</v>
       </c>
-      <c r="B35" s="19"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="39"/>
+      <c r="B35" s="19">
+        <v>9092026</v>
+      </c>
+      <c r="C35" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="D35" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="E35" s="39">
+        <v>3577</v>
+      </c>
+      <c r="F35" s="39">
+        <v>40</v>
+      </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="25">
@@ -5106,6 +5466,1671 @@
       <formula1>"20,40,45,50"</formula1>
     </dataValidation>
   </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14F55FDF-6DCB-4DDA-B827-6D1FD6BE3879}">
+  <dimension ref="A1:M58"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C31,"&lt;&gt;")</f>
+        <v>11</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B36:B45,"&lt;&gt;",C36:C45,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C36:C45)-F2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E36:E45,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>1</v>
+      </c>
+      <c r="B8" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="19">
+        <v>9092026</v>
+      </c>
+      <c r="D8" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="52" t="s">
+        <v>98</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="61"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>2</v>
+      </c>
+      <c r="B9" s="60" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="19">
+        <v>9092026</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="61"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>3</v>
+      </c>
+      <c r="B10" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="19">
+        <v>9092026</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="61"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>4</v>
+      </c>
+      <c r="B11" s="60" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="19">
+        <v>9092026</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" s="61">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>5</v>
+      </c>
+      <c r="B12" s="60" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="19">
+        <v>9092026</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" s="61"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>6</v>
+      </c>
+      <c r="B13" s="60" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13" s="19"/>
+      <c r="D13" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="E13" s="18">
+        <v>313157</v>
+      </c>
+      <c r="F13" s="18">
+        <v>40</v>
+      </c>
+      <c r="G13" s="61"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
+        <v>7</v>
+      </c>
+      <c r="B14" s="60" t="s">
+        <v>113</v>
+      </c>
+      <c r="C14" s="19">
+        <v>9092026</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="61"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
+        <v>8</v>
+      </c>
+      <c r="B15" s="63" t="s">
+        <v>116</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="61"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="17">
+        <v>9</v>
+      </c>
+      <c r="B16" s="64"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="61"/>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
+        <v>10</v>
+      </c>
+      <c r="B17" s="64"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="61"/>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="17">
+        <v>11</v>
+      </c>
+      <c r="B18" s="64"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="61"/>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="17">
+        <v>12</v>
+      </c>
+      <c r="B19" s="64"/>
+      <c r="C19" s="19">
+        <v>9092026</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G19" s="61"/>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="17">
+        <v>13</v>
+      </c>
+      <c r="B20" s="65"/>
+      <c r="C20" s="19">
+        <v>9092026</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="F20" s="18">
+        <v>40</v>
+      </c>
+      <c r="G20" s="61"/>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="17">
+        <v>14</v>
+      </c>
+      <c r="B21" s="60" t="s">
+        <v>129</v>
+      </c>
+      <c r="C21" s="19">
+        <v>9092026</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="F21" s="18">
+        <v>40</v>
+      </c>
+      <c r="G21" s="61"/>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="17">
+        <v>15</v>
+      </c>
+      <c r="B22" s="60" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" s="19">
+        <v>9092026</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="F22" s="18">
+        <v>40</v>
+      </c>
+      <c r="G22" s="61"/>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="17">
+        <v>16</v>
+      </c>
+      <c r="B23" s="60" t="s">
+        <v>135</v>
+      </c>
+      <c r="C23" s="19">
+        <v>9092026</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" s="61"/>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="17">
+        <v>17</v>
+      </c>
+      <c r="B24" s="60" t="s">
+        <v>138</v>
+      </c>
+      <c r="C24" s="19"/>
+      <c r="D24" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="F24" s="18">
+        <v>20</v>
+      </c>
+      <c r="G24" s="61"/>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="17">
+        <v>18</v>
+      </c>
+      <c r="B25" s="42"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="61"/>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="17">
+        <v>19</v>
+      </c>
+      <c r="B26" s="42"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="61"/>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="17">
+        <v>20</v>
+      </c>
+      <c r="B27" s="42"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="61"/>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="17">
+        <v>21</v>
+      </c>
+      <c r="B28" s="42"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="61"/>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="17">
+        <v>22</v>
+      </c>
+      <c r="B29" s="42"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="61"/>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="17">
+        <v>23</v>
+      </c>
+      <c r="B30" s="42"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="61"/>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="17">
+        <v>24</v>
+      </c>
+      <c r="B31" s="42"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="61"/>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="7"/>
+    </row>
+    <row r="33" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="6"/>
+      <c r="B33" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="6"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="25">
+        <v>1</v>
+      </c>
+      <c r="B36" s="19">
+        <v>7092026</v>
+      </c>
+      <c r="C36" s="27"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="25"/>
+    </row>
+    <row r="37" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="25">
+        <v>2</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="58"/>
+      <c r="F37" s="25"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+      <c r="K37" s="31"/>
+      <c r="L37" s="31"/>
+      <c r="M37" s="31"/>
+    </row>
+    <row r="38" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="25">
+        <v>3</v>
+      </c>
+      <c r="B38" s="19"/>
+      <c r="C38" s="27"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="58"/>
+      <c r="F38" s="25"/>
+      <c r="I38" s="31"/>
+      <c r="J38" s="31"/>
+      <c r="K38" s="31"/>
+      <c r="L38" s="31"/>
+      <c r="M38" s="31"/>
+    </row>
+    <row r="39" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="25">
+        <v>4</v>
+      </c>
+      <c r="B39" s="19"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="25"/>
+      <c r="I39" s="31"/>
+      <c r="J39" s="31"/>
+      <c r="K39" s="31"/>
+      <c r="L39" s="31"/>
+      <c r="M39" s="31"/>
+    </row>
+    <row r="40" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="25">
+        <v>5</v>
+      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="25"/>
+      <c r="I40" s="31"/>
+      <c r="J40" s="31"/>
+      <c r="K40" s="31"/>
+      <c r="L40" s="31"/>
+      <c r="M40" s="31"/>
+    </row>
+    <row r="41" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="25">
+        <v>6</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="27"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="25"/>
+      <c r="I41" s="31"/>
+      <c r="J41" s="31"/>
+      <c r="K41" s="31"/>
+      <c r="L41" s="31"/>
+      <c r="M41" s="31"/>
+    </row>
+    <row r="42" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="25">
+        <v>7</v>
+      </c>
+      <c r="B42" s="19"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="25"/>
+      <c r="I42" s="31"/>
+      <c r="J42" s="31"/>
+      <c r="K42" s="31"/>
+      <c r="L42" s="31"/>
+      <c r="M42" s="31"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" s="25">
+        <v>8</v>
+      </c>
+      <c r="B43" s="19"/>
+      <c r="C43" s="27"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="25"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" s="25">
+        <v>9</v>
+      </c>
+      <c r="B44" s="19"/>
+      <c r="C44" s="27"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="25"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" s="25">
+        <v>10</v>
+      </c>
+      <c r="B45" s="19"/>
+      <c r="C45" s="33"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="25"/>
+    </row>
+    <row r="46" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="25">
+        <v>11</v>
+      </c>
+      <c r="B46" s="19"/>
+      <c r="C46" s="33"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="25"/>
+    </row>
+    <row r="47" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="35"/>
+      <c r="B47" s="36"/>
+      <c r="C47" s="37"/>
+      <c r="D47"/>
+      <c r="E47" s="38"/>
+      <c r="F47" s="35"/>
+    </row>
+    <row r="48" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="6"/>
+      <c r="B48" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+    </row>
+    <row r="49" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="6"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E50" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F50" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="25">
+        <v>1</v>
+      </c>
+      <c r="B51" s="19">
+        <v>9092026</v>
+      </c>
+      <c r="C51" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="D51" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="E51" s="39">
+        <v>3577</v>
+      </c>
+      <c r="F51" s="39">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="25">
+        <v>2</v>
+      </c>
+      <c r="B52" s="19"/>
+      <c r="C52" s="28"/>
+      <c r="D52" s="34"/>
+      <c r="E52" s="39"/>
+      <c r="F52" s="39"/>
+    </row>
+    <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="25">
+        <v>3</v>
+      </c>
+      <c r="B53" s="19"/>
+      <c r="C53" s="29"/>
+      <c r="D53" s="29"/>
+      <c r="E53" s="39"/>
+      <c r="F53" s="39"/>
+    </row>
+    <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="25">
+        <v>4</v>
+      </c>
+      <c r="B54" s="19"/>
+      <c r="C54" s="29"/>
+      <c r="D54" s="29"/>
+      <c r="E54" s="39"/>
+      <c r="F54" s="39"/>
+    </row>
+    <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="25">
+        <v>5</v>
+      </c>
+      <c r="B55" s="19"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="39"/>
+      <c r="F55" s="39"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="40">
+        <v>6</v>
+      </c>
+      <c r="B56" s="19"/>
+      <c r="C56" s="25"/>
+      <c r="D56" s="32"/>
+      <c r="E56" s="29"/>
+      <c r="F56" s="29"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="40">
+        <v>7</v>
+      </c>
+      <c r="B57" s="19"/>
+      <c r="C57" s="29"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="29"/>
+      <c r="F57" s="25"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F58" s="41"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B15:B20"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F57 F32" xr:uid="{C60EBE37-60DD-4590-A805-1B082306F56F}">
+      <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F31" xr:uid="{38E0B31F-E63B-4BBF-A034-5D91A0C57AEC}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01E81CCA-C2A4-4E26-88A6-3C25B115BC82}">
+  <dimension ref="A1:M58"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C31,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B36:B45,"&lt;&gt;",C36:C45,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C36:C45)-F2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E36:E45,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>1</v>
+      </c>
+      <c r="B8" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="19"/>
+      <c r="D8" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="52" t="s">
+        <v>98</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="61"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>2</v>
+      </c>
+      <c r="B9" s="60" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="19"/>
+      <c r="D9" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="61"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>3</v>
+      </c>
+      <c r="B10" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="19"/>
+      <c r="D10" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="61"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>4</v>
+      </c>
+      <c r="B11" s="60" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="19"/>
+      <c r="D11" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" s="61"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>5</v>
+      </c>
+      <c r="B12" s="60" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" s="61"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>6</v>
+      </c>
+      <c r="B13" s="60" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13" s="19"/>
+      <c r="D13" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="E13" s="18">
+        <v>313157</v>
+      </c>
+      <c r="F13" s="18">
+        <v>40</v>
+      </c>
+      <c r="G13" s="61"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
+        <v>7</v>
+      </c>
+      <c r="B14" s="60" t="s">
+        <v>113</v>
+      </c>
+      <c r="C14" s="19"/>
+      <c r="D14" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="61"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
+        <v>8</v>
+      </c>
+      <c r="B15" s="63" t="s">
+        <v>116</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="61"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="17">
+        <v>9</v>
+      </c>
+      <c r="B16" s="64"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="61"/>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
+        <v>10</v>
+      </c>
+      <c r="B17" s="64"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="61"/>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="17">
+        <v>11</v>
+      </c>
+      <c r="B18" s="64"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="61"/>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="17">
+        <v>12</v>
+      </c>
+      <c r="B19" s="64"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G19" s="61"/>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="17">
+        <v>13</v>
+      </c>
+      <c r="B20" s="65"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="F20" s="18">
+        <v>40</v>
+      </c>
+      <c r="G20" s="61"/>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="17">
+        <v>14</v>
+      </c>
+      <c r="B21" s="60" t="s">
+        <v>129</v>
+      </c>
+      <c r="C21" s="19"/>
+      <c r="D21" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="F21" s="18">
+        <v>40</v>
+      </c>
+      <c r="G21" s="61"/>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="17">
+        <v>15</v>
+      </c>
+      <c r="B22" s="60" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" s="19"/>
+      <c r="D22" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="F22" s="18">
+        <v>40</v>
+      </c>
+      <c r="G22" s="61"/>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="17">
+        <v>16</v>
+      </c>
+      <c r="B23" s="60" t="s">
+        <v>135</v>
+      </c>
+      <c r="C23" s="19"/>
+      <c r="D23" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" s="61"/>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="17">
+        <v>17</v>
+      </c>
+      <c r="B24" s="60" t="s">
+        <v>138</v>
+      </c>
+      <c r="C24" s="19"/>
+      <c r="D24" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="F24" s="18">
+        <v>20</v>
+      </c>
+      <c r="G24" s="61"/>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="17">
+        <v>18</v>
+      </c>
+      <c r="B25" s="42"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="61"/>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="17">
+        <v>19</v>
+      </c>
+      <c r="B26" s="42"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="61"/>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="17">
+        <v>20</v>
+      </c>
+      <c r="B27" s="42"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="61"/>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="17">
+        <v>21</v>
+      </c>
+      <c r="B28" s="42"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="61"/>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="17">
+        <v>22</v>
+      </c>
+      <c r="B29" s="42"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="61"/>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="17">
+        <v>23</v>
+      </c>
+      <c r="B30" s="42"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="61"/>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="17">
+        <v>24</v>
+      </c>
+      <c r="B31" s="42"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="61"/>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="7"/>
+    </row>
+    <row r="33" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="6"/>
+      <c r="B33" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="6"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="25">
+        <v>1</v>
+      </c>
+      <c r="B36" s="19">
+        <v>7092026</v>
+      </c>
+      <c r="C36" s="27"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="25"/>
+    </row>
+    <row r="37" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="25">
+        <v>2</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="58"/>
+      <c r="F37" s="25"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+      <c r="K37" s="31"/>
+      <c r="L37" s="31"/>
+      <c r="M37" s="31"/>
+    </row>
+    <row r="38" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="25">
+        <v>3</v>
+      </c>
+      <c r="B38" s="19"/>
+      <c r="C38" s="27"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="58"/>
+      <c r="F38" s="25"/>
+      <c r="I38" s="31"/>
+      <c r="J38" s="31"/>
+      <c r="K38" s="31"/>
+      <c r="L38" s="31"/>
+      <c r="M38" s="31"/>
+    </row>
+    <row r="39" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="25">
+        <v>4</v>
+      </c>
+      <c r="B39" s="19"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="25"/>
+      <c r="I39" s="31"/>
+      <c r="J39" s="31"/>
+      <c r="K39" s="31"/>
+      <c r="L39" s="31"/>
+      <c r="M39" s="31"/>
+    </row>
+    <row r="40" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="25">
+        <v>5</v>
+      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="25"/>
+      <c r="I40" s="31"/>
+      <c r="J40" s="31"/>
+      <c r="K40" s="31"/>
+      <c r="L40" s="31"/>
+      <c r="M40" s="31"/>
+    </row>
+    <row r="41" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="25">
+        <v>6</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="27"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="25"/>
+      <c r="I41" s="31"/>
+      <c r="J41" s="31"/>
+      <c r="K41" s="31"/>
+      <c r="L41" s="31"/>
+      <c r="M41" s="31"/>
+    </row>
+    <row r="42" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="25">
+        <v>7</v>
+      </c>
+      <c r="B42" s="19"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="25"/>
+      <c r="I42" s="31"/>
+      <c r="J42" s="31"/>
+      <c r="K42" s="31"/>
+      <c r="L42" s="31"/>
+      <c r="M42" s="31"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" s="25">
+        <v>8</v>
+      </c>
+      <c r="B43" s="19"/>
+      <c r="C43" s="27"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="25"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" s="25">
+        <v>9</v>
+      </c>
+      <c r="B44" s="19"/>
+      <c r="C44" s="27"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="25"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" s="25">
+        <v>10</v>
+      </c>
+      <c r="B45" s="19"/>
+      <c r="C45" s="33"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="25"/>
+    </row>
+    <row r="46" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="25">
+        <v>11</v>
+      </c>
+      <c r="B46" s="19"/>
+      <c r="C46" s="33"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="25"/>
+    </row>
+    <row r="47" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="35"/>
+      <c r="B47" s="36"/>
+      <c r="C47" s="37"/>
+      <c r="D47"/>
+      <c r="E47" s="38"/>
+      <c r="F47" s="35"/>
+    </row>
+    <row r="48" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="6"/>
+      <c r="B48" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+    </row>
+    <row r="49" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="6"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E50" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F50" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="25">
+        <v>1</v>
+      </c>
+      <c r="B51" s="19">
+        <v>9092026</v>
+      </c>
+      <c r="C51" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="D51" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="E51" s="39">
+        <v>3577</v>
+      </c>
+      <c r="F51" s="39">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="25">
+        <v>2</v>
+      </c>
+      <c r="B52" s="19"/>
+      <c r="C52" s="28"/>
+      <c r="D52" s="34"/>
+      <c r="E52" s="39"/>
+      <c r="F52" s="39"/>
+    </row>
+    <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="25">
+        <v>3</v>
+      </c>
+      <c r="B53" s="19"/>
+      <c r="C53" s="29"/>
+      <c r="D53" s="29"/>
+      <c r="E53" s="39"/>
+      <c r="F53" s="39"/>
+    </row>
+    <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="25">
+        <v>4</v>
+      </c>
+      <c r="B54" s="19"/>
+      <c r="C54" s="29"/>
+      <c r="D54" s="29"/>
+      <c r="E54" s="39"/>
+      <c r="F54" s="39"/>
+    </row>
+    <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="25">
+        <v>5</v>
+      </c>
+      <c r="B55" s="19"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="39"/>
+      <c r="F55" s="39"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="40">
+        <v>6</v>
+      </c>
+      <c r="B56" s="19"/>
+      <c r="C56" s="25"/>
+      <c r="D56" s="32"/>
+      <c r="E56" s="29"/>
+      <c r="F56" s="29"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="40">
+        <v>7</v>
+      </c>
+      <c r="B57" s="19"/>
+      <c r="C57" s="29"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="29"/>
+      <c r="F57" s="25"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F58" s="41"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B15:B20"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F26 F28:F31" xr:uid="{6AE38A2C-D536-43A6-874D-A17F73BC6B4C}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F57 F32" xr:uid="{2C76199B-A1FF-4695-A4B3-E9AFCFD4BC11}">
+      <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
